--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4828" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4827" uniqueCount="599">
   <si>
     <t>Property</t>
   </si>
@@ -1104,8 +1104,7 @@
 </t>
   </si>
   <si>
-    <t>観察対象者  
-【JP Core仕様】患者情報</t>
+    <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
     <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
@@ -1133,8 +1132,7 @@
 </t>
   </si>
   <si>
-    <t>subject 要素が実際のobservationの対象でない場合に、observation の対象物。  
-【JP Core仕様】未使用</t>
+    <t>subject 要素が実際のobservationの対象でない場合に、observation の対象物。  【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
@@ -1186,8 +1184,7 @@
 </t>
   </si>
   <si>
-    <t>臨床的に関連する時刻または時間  
-【JP Core仕様】実施日時</t>
+    <t>臨床的に関連する時刻または時間  【JP Core仕様】実施日時</t>
   </si>
   <si>
     <t>この観察結果が過去の報告でない限り、少なくとも日付が存在する必要がある。不正確または「あいまいな」時間を記録するには（たとえば、「朝食後」に行われた血糖測定）、[Timing]（datatypes.html＃timing）データ型を使用して、測定を通常のライフイベントに関連付けることができる。</t>
@@ -1215,8 +1212,7 @@
 </t>
   </si>
   <si>
-    <t>このバージョンが利用可能となった日時  
-【JP Core仕様】所見確定日時</t>
+    <t>このバージョンが利用可能となった日時  【JP Core仕様】所見確定日時</t>
   </si>
   <si>
     <t>レビューと検証を必要としないobservationの場合、リソース自体の[`lastUpdated`]（resource-definitions.html＃Meta.lastUpdated）日時と同じになる場合がある。特定の更新のレビューと検証が必要なobservationの場合、新しいバージョンを再度レビューして検証する必要がないような臨床的に重要でない更新がなされたために、リソース自体の「lastUpdated」時間はこれと異なる場合がある。</t>
@@ -1262,8 +1258,7 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>実際の結果値  
-【JP Core仕様】component要素を利用して複数の結果を表現することを考慮しているため、本要素は使用しない</t>
+    <t>実際の結果値  【JP Core仕様】component要素を利用して複数の結果を表現することを考慮しているため、本要素は使用しない</t>
   </si>
   <si>
     <t>観察にはあります。1）ここでの単一の値、2）関連する値とコンポーネント値のセット、または3）関連またはコンポーネント値のセットのみ。値が存在する場合、この要素のデータ型は、viscervation.codeによって決定する必要があります。フィールドが通常コーディングされている場合、または観測に関連付けられたタイプの場合、文字列の代わりにテキストのみを持つCodeableconecteが使用されます。コードはコード化された値を定義します。追加のガイダンスについては、以下の[[メモ]セクション]（[観察.html＃注）を参照してください。 / An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -1291,8 +1286,7 @@
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
-    <t>結果が欠損値である理由  
-【JP Core仕様】結果が存在しなかった場合、その理由</t>
+    <t>結果が欠損値である理由  【JP Core仕様】結果が存在しなかった場合、その理由</t>
   </si>
   <si>
     <t>ヌル値または例外値は、FHIRオブザベーションで2つの方法で表すことができる。 1つの方法は、それらを値セットに含めて、値の例外を表す方法である。たとえば、血清学的検査の測定値は、「検出された」、「検出されなかった」、「決定的でない」、または「検体が不十分」である可能性がある。別の方法は、実際の観測にvalue要素を使用し、明示的なdataAbsentReason要素を使用して例外的な値を記録することである。たとえば、測定が完了しなかった場合、dataAbsentReasonコード「error」を使用できる。この場合には、観測値は、報告する値がある場合にのみ報告される可能性があることに注意する必要がある。たとえば、差分セルカウント値は&gt; 0の場合にのみ報告される場合がある。これらのオプションのため、nullまたは例外値の一般的な観測値を解釈するにはユースケースの合意が必要である。</t>
@@ -1324,8 +1318,7 @@
 </t>
   </si>
   <si>
-    <t>高、低、正常等の結果のカテゴリ分けした評価
-【JP Core仕様】未使用</t>
+    <t>高、低、正常等の結果のカテゴリ分けした評価【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>「異常フラグ」として呼ばれる検査結果解釈コードが従来から使用されており、その使用はコード化された解釈が関連するような他の場合でも拡大して使われている。多くの場合、1つ以上の単純でコンパクトなコードとして報告され、この要素は、結果の意味や正常かどうかを示すために、レポートや時系列表で結果値の隣に配置されることがよくある。</t>
@@ -1359,8 +1352,7 @@
 </t>
   </si>
   <si>
-    <t>結果に対するコメント  
-【JP Core仕様】未使用</t>
+    <t>結果に対するコメント  【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>観察（結果）に関する一般的な記述、重要な、予期しない、または信頼できない結果値に関する記述、またはその解釈に関連する場合はそのソースに関する情報が含まれる場合がある。</t>
@@ -1379,8 +1371,7 @@
     <t>Observation.bodySite</t>
   </si>
   <si>
-    <t>観察された身体部位  
-【JP Core仕様】特定の歯（歯式）を指定</t>
+    <t>観察された身体部位  【JP Core仕様】特定の歯（歯式）を指定</t>
   </si>
   <si>
     <t>観察結果で見つかったコードで暗黙的ではない場合にのみ使用されます。多くのシステムでは、これはインラインコンポーネントの代わりに関連する観察として表される場合があります。
@@ -1388,10 +1379,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalBodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1437,8 +1425,7 @@
 </t>
   </si>
   <si>
-    <t>観察（観測、検査）に使われた検体材料
-【JP Core仕様】未使用</t>
+    <t>観察（観測、検査）に使われた検体材料 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>`Observation.code`にあるコードで暗黙的に示されない場合にのみ使用する必要がある。検体自体の観察は行われない。観察（観測、検査）対象者に対して実施されるが、多くの場合には対象者から得られた検体に対して実施される。検体が奥の場合に関わるが、それらは常に追跡され、明示的に報告されるとは限らないことに注意すること。またobservationリソースは、検体を明示的に記述するような状況下（診断レポートなど）で使用される場合があることに注意。</t>
@@ -1677,8 +1664,7 @@
 </t>
   </si>
   <si>
-    <t>observationの発生源に関連する測定
-【JP Core仕様】未使用</t>
+    <t>observationの発生源に関連する測定 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>この要素にリストされているすべての参照の選択肢は、派生値の元のデータなる可能性のある臨床観察やその他の測定値を表すことができる。最も一般的な参照先は、別のobservationである。observationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照すること。</t>
@@ -1690,8 +1676,7 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>複合的な結果
-【JP Core仕様】欠損歯の処置状態</t>
+    <t>複合的な結果 【JP Core仕様】欠損歯の処置状態</t>
   </si>
   <si>
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
@@ -11131,13 +11116,11 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="Y74" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y74" s="2"/>
+      <c r="Z74" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11173,27 +11156,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>442</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11219,16 +11202,16 @@
         <v>191</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11256,11 +11239,11 @@
         <v>325</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
       </c>
@@ -11277,7 +11260,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11298,10 +11281,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11312,10 +11295,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11338,16 +11321,16 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11397,7 +11380,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11415,27 +11398,27 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>458</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11458,16 +11441,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11517,7 +11500,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11535,27 +11518,27 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>466</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11566,7 +11549,7 @@
         <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>83</v>
@@ -11578,19 +11561,19 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M78" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11639,7 +11622,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11651,19 +11634,19 @@
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AK78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AN78" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11674,10 +11657,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11792,10 +11775,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11912,14 +11895,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11941,10 +11924,10 @@
         <v>140</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>143</v>
@@ -11999,7 +11982,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12034,10 +12017,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12060,13 +12043,13 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12117,7 +12100,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12126,7 +12109,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -12138,10 +12121,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12152,10 +12135,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12178,13 +12161,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12235,7 +12218,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12244,7 +12227,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12256,10 +12239,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12270,10 +12253,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12299,16 +12282,16 @@
         <v>191</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12336,11 +12319,11 @@
         <v>118</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
       </c>
@@ -12357,7 +12340,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12375,10 +12358,10 @@
         <v>83</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>425</v>
@@ -12392,10 +12375,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12421,16 +12404,16 @@
         <v>191</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12458,11 +12441,11 @@
         <v>325</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>508</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
       </c>
@@ -12479,7 +12462,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12497,10 +12480,10 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>425</v>
@@ -12514,10 +12497,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12540,17 +12523,17 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12599,7 +12582,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12623,7 +12606,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12634,10 +12617,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12663,10 +12646,10 @@
         <v>208</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12717,7 +12700,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12738,10 +12721,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12752,10 +12735,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12766,7 +12749,7 @@
         <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>83</v>
@@ -12778,16 +12761,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12837,7 +12820,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12858,10 +12841,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12872,10 +12855,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12898,16 +12881,16 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12957,7 +12940,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12978,10 +12961,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12992,10 +12975,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13018,19 +13001,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13079,7 +13062,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13100,10 +13083,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13114,10 +13097,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13232,10 +13215,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13352,14 +13335,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13381,10 +13364,10 @@
         <v>140</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>143</v>
@@ -13439,7 +13422,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13474,10 +13457,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13503,13 +13486,13 @@
         <v>191</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>324</v>
@@ -13561,7 +13544,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>94</v>
@@ -13579,7 +13562,7 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>330</v>
@@ -13596,10 +13579,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13714,10 +13697,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13834,10 +13817,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13909,7 +13892,7 @@
         <v>83</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AC97" s="2"/>
       <c r="AD97" t="s" s="2">
@@ -13954,10 +13937,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14072,10 +14055,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14192,10 +14175,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14314,10 +14297,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14434,10 +14417,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14554,10 +14537,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14674,10 +14657,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14796,13 +14779,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C105" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>83</v>
@@ -14827,10 +14810,10 @@
         <v>221</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>224</v>
@@ -14865,7 +14848,7 @@
       </c>
       <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -14918,10 +14901,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15036,10 +15019,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15156,10 +15139,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15201,7 +15184,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>83</v>
@@ -15278,10 +15261,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15398,10 +15381,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15518,10 +15501,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15638,10 +15621,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15760,13 +15743,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C113" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>83</v>
@@ -15791,10 +15774,10 @@
         <v>221</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>224</v>
@@ -15829,7 +15812,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>83</v>
@@ -15882,10 +15865,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16000,10 +15983,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16120,10 +16103,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16165,7 +16148,7 @@
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>83</v>
@@ -16242,10 +16225,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16362,10 +16345,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16482,10 +16465,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16602,10 +16585,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16724,10 +16707,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16846,10 +16829,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16872,16 +16855,16 @@
         <v>95</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>401</v>
@@ -16933,7 +16916,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -16951,7 +16934,7 @@
         <v>83</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>404</v>
@@ -16968,10 +16951,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16997,13 +16980,13 @@
         <v>191</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>410</v>
@@ -17055,7 +17038,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17090,10 +17073,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17119,16 +17102,16 @@
         <v>191</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -17177,7 +17160,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -17212,10 +17195,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17241,16 +17224,16 @@
         <v>84</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>83</v>
@@ -17299,7 +17282,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -17320,10 +17303,10 @@
         <v>83</v>
       </c>
       <c r="AM125" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>83</v>
